--- a/api/templates/module_swaps/fr.xlsx
+++ b/api/templates/module_swaps/fr.xlsx
@@ -1,42 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/module_swaps/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F424E6FE-0056-3E49-9BC5-4ECD56EA0A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Results" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>Échanges de modules</t>
+  </si>
+  <si>
+    <t>Plage de dates : &lt;Dates&gt;</t>
+  </si>
   <si>
     <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
   </si>
@@ -47,12 +31,54 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
+    <t>Pourcentage d’échanges de modules dans le cadre du SLA :</t>
+  </si>
+  <si>
+    <t>Nombre total d’échanges :</t>
+  </si>
+  <si>
+    <t>Nombre de sites ayant fait l’objet d’échanges :</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Nom de l’appareil</t>
+  </si>
+  <si>
+    <t>Nom du site</t>
+  </si>
+  <si>
+    <t>Date du dernier résultat sur l’ancien module</t>
+  </si>
+  <si>
+    <t>Date du premier résultat sur le nouveau module</t>
+  </si>
+  <si>
+    <t>Nombre de jours entre ces dates</t>
+  </si>
+  <si>
+    <t>Série de l’instrument</t>
+  </si>
+  <si>
+    <t>Ancien module série</t>
+  </si>
+  <si>
+    <t>Nouveau module série</t>
+  </si>
+  <si>
+    <t>Baie de module</t>
+  </si>
+  <si>
     <t>&lt;deviceName&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;lastResultOldModule&gt;</t>
   </si>
   <si>
@@ -72,108 +98,63 @@
   </si>
   <si>
     <t>&lt;moduleName&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
-  </si>
-  <si>
-    <t>Échanges de modules</t>
-  </si>
-  <si>
-    <t>Plage de dates : &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Pourcentage d’échanges de modules dans le cadre du SLA :</t>
-  </si>
-  <si>
-    <t>Nombre total d’échanges :</t>
-  </si>
-  <si>
-    <t>Nombre de sites ayant fait l’objet d’échanges :</t>
-  </si>
-  <si>
-    <t>Nom de l’appareil</t>
-  </si>
-  <si>
-    <t>Nom du site</t>
-  </si>
-  <si>
-    <t>Date du dernier résultat sur l’ancien module</t>
-  </si>
-  <si>
-    <t>Date du premier résultat sur le nouveau module</t>
-  </si>
-  <si>
-    <t>Nombre de jours entre ces dates</t>
-  </si>
-  <si>
-    <t>Série de l’instrument</t>
-  </si>
-  <si>
-    <t>Ancien module série</t>
-  </si>
-  <si>
-    <t>Nouveau module série</t>
-  </si>
-  <si>
-    <t>Baie de module</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -199,114 +180,98 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBF30B"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -314,83 +279,8 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBF30B"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFBF30B"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -698,206 +588,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.1640625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="23.1640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="25" customWidth="1"/>
-    <col min="8" max="8" width="28" style="15" customWidth="1"/>
-    <col min="9" max="9" width="18.5" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.1640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-    </row>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="19"/>
+    <row r="1" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="14"/>
-      <c r="G2" s="24"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="19"/>
+    <row r="3" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="24"/>
+      <c r="G3" s="15"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="19"/>
+    <row r="4" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="24"/>
+      <c r="G4" s="15"/>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="19"/>
+    <row r="5" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
       <c r="F5" s="14"/>
-      <c r="G5" s="24"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
     </row>
-    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="19"/>
+    <row r="6" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
       <c r="F6" s="14"/>
-      <c r="G6" s="24"/>
+      <c r="G6" s="15"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
     </row>
-    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="30" t="str">
+    <row r="7" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="str">
         <f>TEXT(COUNTIF(E12:E10002,"&lt;=8")/COUNTIF(E12:E10002,"&lt;&gt;"),"0%")</f>
         <v>0%</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="14"/>
-      <c r="G7" s="24"/>
+      <c r="G7" s="15"/>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="19"/>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="24"/>
+      <c r="G10" s="15"/>
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="1:9" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" ht="31" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="29" t="s">
+    </row>
+    <row r="12" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="B12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="C12" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="D12" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="E12" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="F12" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="G12" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="27" t="s">
+      <c r="H12" s="28" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>11</v>
+      <c r="I12" s="28" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D10 E12 D13:D1000001">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/module_swaps/fr.xlsx
+++ b/api/templates/module_swaps/fr.xlsx
@@ -226,9 +226,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/api/templates/module_swaps/fr.xlsx
+++ b/api/templates/module_swaps/fr.xlsx
@@ -31,7 +31,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>Pourcentage d’échanges de modules dans le cadre du SLA :</t>
@@ -226,7 +226,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
